--- a/research/traditional_assets/database/data/greece/greece_entertainment.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_entertainment.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.325</v>
+        <v>0.261</v>
       </c>
       <c r="G2">
-        <v>-0.005751295336787565</v>
+        <v>-0.00556541019955654</v>
       </c>
       <c r="H2">
-        <v>-0.005751295336787565</v>
+        <v>-0.00556541019955654</v>
       </c>
       <c r="I2">
-        <v>-0.009378238341968912</v>
+        <v>-0.03052475979305247</v>
       </c>
       <c r="J2">
-        <v>-0.009378238341968912</v>
+        <v>-0.03052475979305247</v>
       </c>
       <c r="K2">
-        <v>1.57</v>
+        <v>-6.16</v>
       </c>
       <c r="L2">
-        <v>0.008134715025906736</v>
+        <v>-0.04552845528455284</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.57</v>
+        <v>4.67</v>
       </c>
       <c r="V2">
-        <v>0.05836526181353768</v>
+        <v>0.05318906605922551</v>
       </c>
       <c r="W2">
-        <v>-0.7201834862385321</v>
+        <v>-2.566666666666667</v>
       </c>
       <c r="X2">
-        <v>0.1548987193016944</v>
+        <v>0.2396226410327308</v>
       </c>
       <c r="Y2">
-        <v>-0.8750822055402265</v>
+        <v>-2.806289307699398</v>
       </c>
       <c r="Z2">
-        <v>3.379443179828401</v>
+        <v>2.108790523690773</v>
       </c>
       <c r="AA2">
-        <v>-0.03169322360357205</v>
+        <v>-0.06437032418952617</v>
       </c>
       <c r="AB2">
-        <v>0.1031983667196566</v>
+        <v>0.1738980268993018</v>
       </c>
       <c r="AC2">
-        <v>-0.1348915903232287</v>
+        <v>-0.2382683510888279</v>
       </c>
       <c r="AD2">
-        <v>69</v>
+        <v>56.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>69</v>
+        <v>56.2</v>
       </c>
       <c r="AG2">
-        <v>64.43000000000001</v>
+        <v>51.53</v>
       </c>
       <c r="AH2">
-        <v>0.4684317718940936</v>
+        <v>0.3902777777777778</v>
       </c>
       <c r="AI2">
-        <v>0.8679245283018868</v>
+        <v>0.9330898223476672</v>
       </c>
       <c r="AJ2">
-        <v>0.4514117564632523</v>
+        <v>0.3698413837651619</v>
       </c>
       <c r="AK2">
-        <v>0.8598692112638463</v>
+        <v>0.9274658027357812</v>
       </c>
       <c r="AL2">
-        <v>5.49</v>
+        <v>5.81</v>
       </c>
       <c r="AM2">
-        <v>5.49</v>
+        <v>5.718999999999999</v>
       </c>
       <c r="AN2">
-        <v>-47.26027397260274</v>
+        <v>-15.3133514986376</v>
       </c>
       <c r="AO2">
-        <v>-0.3296903460837887</v>
+        <v>-0.710843373493976</v>
       </c>
       <c r="AP2">
-        <v>-44.13013698630137</v>
+        <v>-14.0408719346049</v>
       </c>
       <c r="AQ2">
-        <v>-0.3296903460837887</v>
+        <v>-0.7221542227662179</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.325</v>
+        <v>0.261</v>
       </c>
       <c r="G3">
-        <v>-0.005751295336787565</v>
+        <v>-0.00556541019955654</v>
       </c>
       <c r="H3">
-        <v>-0.005751295336787565</v>
+        <v>-0.00556541019955654</v>
       </c>
       <c r="I3">
-        <v>-0.009378238341968912</v>
+        <v>-0.03052475979305247</v>
       </c>
       <c r="J3">
-        <v>-0.009378238341968912</v>
+        <v>-0.03052475979305247</v>
       </c>
       <c r="K3">
-        <v>1.57</v>
+        <v>-6.16</v>
       </c>
       <c r="L3">
-        <v>0.008134715025906736</v>
+        <v>-0.04552845528455284</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.57</v>
+        <v>4.67</v>
       </c>
       <c r="V3">
-        <v>0.05836526181353768</v>
+        <v>0.05318906605922551</v>
       </c>
       <c r="W3">
-        <v>-0.7201834862385321</v>
+        <v>-2.566666666666667</v>
       </c>
       <c r="X3">
-        <v>0.1548987193016944</v>
+        <v>0.2396226410327308</v>
       </c>
       <c r="Y3">
-        <v>-0.8750822055402265</v>
+        <v>-2.806289307699398</v>
       </c>
       <c r="Z3">
-        <v>3.379443179828401</v>
+        <v>2.108790523690773</v>
       </c>
       <c r="AA3">
-        <v>-0.03169322360357205</v>
+        <v>-0.06437032418952617</v>
       </c>
       <c r="AB3">
-        <v>0.1031983667196566</v>
+        <v>0.1738980268993018</v>
       </c>
       <c r="AC3">
-        <v>-0.1348915903232287</v>
+        <v>-0.2382683510888279</v>
       </c>
       <c r="AD3">
-        <v>69</v>
+        <v>56.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>69</v>
+        <v>56.2</v>
       </c>
       <c r="AG3">
-        <v>64.43000000000001</v>
+        <v>51.53</v>
       </c>
       <c r="AH3">
-        <v>0.4684317718940936</v>
+        <v>0.3902777777777778</v>
       </c>
       <c r="AI3">
-        <v>0.8679245283018868</v>
+        <v>0.9330898223476672</v>
       </c>
       <c r="AJ3">
-        <v>0.4514117564632523</v>
+        <v>0.3698413837651619</v>
       </c>
       <c r="AK3">
-        <v>0.8598692112638463</v>
+        <v>0.9274658027357812</v>
       </c>
       <c r="AL3">
-        <v>5.49</v>
+        <v>5.81</v>
       </c>
       <c r="AM3">
-        <v>5.49</v>
+        <v>5.718999999999999</v>
       </c>
       <c r="AN3">
-        <v>-47.26027397260274</v>
+        <v>-15.3133514986376</v>
       </c>
       <c r="AO3">
-        <v>-0.3296903460837887</v>
+        <v>-0.710843373493976</v>
       </c>
       <c r="AP3">
-        <v>-44.13013698630137</v>
+        <v>-14.0408719346049</v>
       </c>
       <c r="AQ3">
-        <v>-0.3296903460837887</v>
+        <v>-0.7221542227662179</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/greece/greece_entertainment.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_entertainment.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.261</v>
+        <v>0.282</v>
       </c>
       <c r="G2">
-        <v>-0.00556541019955654</v>
+        <v>-0.02029355456285897</v>
       </c>
       <c r="H2">
-        <v>-0.00556541019955654</v>
+        <v>-0.02029355456285897</v>
       </c>
       <c r="I2">
-        <v>-0.03052475979305247</v>
+        <v>-0.0391193363114231</v>
       </c>
       <c r="J2">
-        <v>-0.03052475979305247</v>
+        <v>-0.0391193363114231</v>
       </c>
       <c r="K2">
-        <v>-6.16</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.04552845528455284</v>
+        <v>-0.0603063178047224</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.67</v>
+        <v>0.642</v>
       </c>
       <c r="V2">
-        <v>0.05318906605922551</v>
+        <v>0.007430555555555555</v>
       </c>
       <c r="W2">
-        <v>-2.566666666666667</v>
+        <v>3.118811881188119</v>
       </c>
       <c r="X2">
-        <v>0.2396226410327308</v>
+        <v>0.150406878397699</v>
       </c>
       <c r="Y2">
-        <v>-2.806289307699398</v>
+        <v>2.96840500279042</v>
       </c>
       <c r="Z2">
-        <v>2.108790523690773</v>
+        <v>3.38591184096802</v>
       </c>
       <c r="AA2">
-        <v>-0.06437032418952617</v>
+        <v>-0.1324546240276577</v>
       </c>
       <c r="AB2">
-        <v>0.1738980268993018</v>
+        <v>0.1225975885072303</v>
       </c>
       <c r="AC2">
-        <v>-0.2382683510888279</v>
+        <v>-0.2550522125348881</v>
       </c>
       <c r="AD2">
-        <v>56.2</v>
+        <v>36.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>56.2</v>
+        <v>36.3</v>
       </c>
       <c r="AG2">
-        <v>51.53</v>
+        <v>35.65799999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3902777777777778</v>
+        <v>0.2958435207823961</v>
       </c>
       <c r="AI2">
-        <v>0.9330898223476672</v>
+        <v>1.390804597701149</v>
       </c>
       <c r="AJ2">
-        <v>0.3698413837651619</v>
+        <v>0.2921398023890281</v>
       </c>
       <c r="AK2">
-        <v>0.9274658027357812</v>
+        <v>1.400659910440726</v>
       </c>
       <c r="AL2">
-        <v>5.81</v>
+        <v>4.17</v>
       </c>
       <c r="AM2">
-        <v>5.718999999999999</v>
+        <v>3.589</v>
       </c>
       <c r="AN2">
-        <v>-15.3133514986376</v>
+        <v>-6.280276816608996</v>
       </c>
       <c r="AO2">
-        <v>-0.710843373493976</v>
+        <v>-1.470023980815348</v>
       </c>
       <c r="AP2">
-        <v>-14.0408719346049</v>
+        <v>-6.169204152249134</v>
       </c>
       <c r="AQ2">
-        <v>-0.7221542227662179</v>
+        <v>-1.707996656450265</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.261</v>
+        <v>0.282</v>
       </c>
       <c r="G3">
-        <v>-0.00556541019955654</v>
+        <v>-0.02029355456285897</v>
       </c>
       <c r="H3">
-        <v>-0.00556541019955654</v>
+        <v>-0.02029355456285897</v>
       </c>
       <c r="I3">
-        <v>-0.03052475979305247</v>
+        <v>-0.0391193363114231</v>
       </c>
       <c r="J3">
-        <v>-0.03052475979305247</v>
+        <v>-0.0391193363114231</v>
       </c>
       <c r="K3">
-        <v>-6.16</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.04552845528455284</v>
+        <v>-0.0603063178047224</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.67</v>
+        <v>0.642</v>
       </c>
       <c r="V3">
-        <v>0.05318906605922551</v>
+        <v>0.007430555555555555</v>
       </c>
       <c r="W3">
-        <v>-2.566666666666667</v>
+        <v>3.118811881188119</v>
       </c>
       <c r="X3">
-        <v>0.2396226410327308</v>
+        <v>0.150406878397699</v>
       </c>
       <c r="Y3">
-        <v>-2.806289307699398</v>
+        <v>2.96840500279042</v>
       </c>
       <c r="Z3">
-        <v>2.108790523690773</v>
+        <v>3.38591184096802</v>
       </c>
       <c r="AA3">
-        <v>-0.06437032418952617</v>
+        <v>-0.1324546240276577</v>
       </c>
       <c r="AB3">
-        <v>0.1738980268993018</v>
+        <v>0.1225975885072303</v>
       </c>
       <c r="AC3">
-        <v>-0.2382683510888279</v>
+        <v>-0.2550522125348881</v>
       </c>
       <c r="AD3">
-        <v>56.2</v>
+        <v>36.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>56.2</v>
+        <v>36.3</v>
       </c>
       <c r="AG3">
-        <v>51.53</v>
+        <v>35.65799999999999</v>
       </c>
       <c r="AH3">
-        <v>0.3902777777777778</v>
+        <v>0.2958435207823961</v>
       </c>
       <c r="AI3">
-        <v>0.9330898223476672</v>
+        <v>1.390804597701149</v>
       </c>
       <c r="AJ3">
-        <v>0.3698413837651619</v>
+        <v>0.2921398023890281</v>
       </c>
       <c r="AK3">
-        <v>0.9274658027357812</v>
+        <v>1.400659910440726</v>
       </c>
       <c r="AL3">
-        <v>5.81</v>
+        <v>4.17</v>
       </c>
       <c r="AM3">
-        <v>5.718999999999999</v>
+        <v>3.589</v>
       </c>
       <c r="AN3">
-        <v>-15.3133514986376</v>
+        <v>-6.280276816608996</v>
       </c>
       <c r="AO3">
-        <v>-0.710843373493976</v>
+        <v>-1.470023980815348</v>
       </c>
       <c r="AP3">
-        <v>-14.0408719346049</v>
+        <v>-6.169204152249134</v>
       </c>
       <c r="AQ3">
-        <v>-0.7221542227662179</v>
+        <v>-1.707996656450265</v>
       </c>
     </row>
   </sheetData>
